--- a/data/trans_orig/Q5401-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q5401-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si son capaces de realizar las tareas de la casa en 2007</t>
+          <t>Población según si son capaces de realizar las tareas de la casa en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4100</t>
+          <t>3822</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7945</t>
+          <t>9112</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>916</t>
+          <t>937</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8892</t>
+          <t>9003</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,07%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3953</t>
+          <t>3637</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13014</t>
+          <t>13816</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>39,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2384</t>
+          <t>3165</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12557</t>
+          <t>13071</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8788</t>
+          <t>8605</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22328</t>
+          <t>22216</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>29,77%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21438</t>
+          <t>20120</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30943</t>
+          <t>30836</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>60,58%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24301</t>
+          <t>22723</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>34753</t>
+          <t>34745</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>61,94%</t>
+          <t>57,92%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>48340</t>
+          <t>48378</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>63334</t>
+          <t>62798</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>64,78%</t>
+          <t>64,83%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>84,16%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10846</t>
+          <t>11637</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>3127</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14165</t>
+          <t>14231</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7885</t>
+          <t>6964</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>22423</t>
+          <t>21629</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,15%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3054</t>
+          <t>3328</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14535</t>
+          <t>14227</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7545</t>
+          <t>7601</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21515</t>
+          <t>22065</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>14041</t>
+          <t>12721</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>30976</t>
+          <t>30969</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,82%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>45894</t>
+          <t>44806</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>58790</t>
+          <t>58334</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>68,85%</t>
+          <t>67,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>67826</t>
+          <t>68672</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>84488</t>
+          <t>85196</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>70,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>118972</t>
+          <t>119070</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>139892</t>
+          <t>140058</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>85,13%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>891</t>
+          <t>881</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8168</t>
+          <t>7583</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3209</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>14287</t>
+          <t>14068</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4338</t>
+          <t>5041</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>17018</t>
+          <t>17910</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>13,32%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3643</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13682</t>
+          <t>14001</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18570</t>
+          <t>18430</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36232</t>
+          <t>36145</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25795</t>
+          <t>25920</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>45308</t>
+          <t>44930</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>33,41%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>34105</t>
+          <t>34469</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>45271</t>
+          <t>45262</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>40632</t>
+          <t>40322</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>58391</t>
+          <t>58646</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>70,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>78491</t>
+          <t>79550</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>99760</t>
+          <t>99861</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>74,27%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>817</t>
+          <t>820</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6952</t>
+          <t>7088</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3067</t>
+          <t>3077</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13730</t>
+          <t>13281</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4952</t>
+          <t>5229</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16489</t>
+          <t>17201</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>13,29%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3389</t>
+          <t>3821</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14058</t>
+          <t>14512</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10775</t>
+          <t>11232</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25055</t>
+          <t>25787</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17937</t>
+          <t>17914</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>36317</t>
+          <t>35881</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>27,72%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>38568</t>
+          <t>37676</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>49740</t>
+          <t>49639</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>68,35%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>41646</t>
+          <t>40504</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>57282</t>
+          <t>57177</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>54,5%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>76,94%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>83661</t>
+          <t>83959</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>102540</t>
+          <t>103659</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>80,08%</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5909</t>
+          <t>6057</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>939</t>
+          <t>894</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8228</t>
+          <t>8392</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1839</t>
+          <t>1724</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11243</t>
+          <t>10095</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>14,3%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2407</t>
+          <t>1826</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10400</t>
+          <t>9791</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6203</t>
+          <t>5629</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>17401</t>
+          <t>16803</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>9338</t>
+          <t>9736</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>22953</t>
+          <t>23603</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>33,44%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17111</t>
+          <t>17778</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>25977</t>
+          <t>26020</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>58,31%</t>
+          <t>60,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20766</t>
+          <t>21087</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32947</t>
+          <t>33046</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>51,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>42399</t>
+          <t>41890</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>57152</t>
+          <t>56825</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>59,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>80,5%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1885</t>
+          <t>2679</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10492</t>
+          <t>11162</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2282</t>
+          <t>2339</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12354</t>
+          <t>12673</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6328</t>
+          <t>6248</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>20380</t>
+          <t>19823</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>16,87%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6771</t>
+          <t>6605</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18446</t>
+          <t>17632</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13029</t>
+          <t>12599</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>28697</t>
+          <t>28497</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>21556</t>
+          <t>22280</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>41912</t>
+          <t>41324</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>35,17%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>23289</t>
+          <t>22547</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>36024</t>
+          <t>35834</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>47,77%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>75,93%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>35645</t>
+          <t>36438</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>52742</t>
+          <t>51995</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>51,82%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>62646</t>
+          <t>65051</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>84669</t>
+          <t>84347</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>53,31%</t>
+          <t>55,36%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>72,06%</t>
+          <t>71,78%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>813</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7196</t>
+          <t>7285</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2831</t>
+          <t>2965</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>13455</t>
+          <t>13246</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4957</t>
+          <t>4637</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>16380</t>
+          <t>16407</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,36%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>8098</t>
+          <t>7238</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>22412</t>
+          <t>21386</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>21423</t>
+          <t>19884</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>40345</t>
+          <t>39739</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>32080</t>
+          <t>30372</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>55612</t>
+          <t>55217</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,76%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>81301</t>
+          <t>81679</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>95976</t>
+          <t>96826</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>70377</t>
+          <t>71304</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>90143</t>
+          <t>90627</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>60,88%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>77,38%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>157286</t>
+          <t>158113</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>182986</t>
+          <t>183803</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>70,89%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>82,4%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>3479</t>
+          <t>3754</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>13431</t>
+          <t>14637</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>4231</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>17288</t>
+          <t>17743</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>9988</t>
+          <t>10547</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>26012</t>
+          <t>26745</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>10,09%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>15617</t>
+          <t>15677</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>32804</t>
+          <t>32398</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>23737</t>
+          <t>24057</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>44409</t>
+          <t>46006</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>43672</t>
+          <t>44682</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>72048</t>
+          <t>72317</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,28%</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>71157</t>
+          <t>71998</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>89567</t>
+          <t>89326</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>64,35%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>80,05%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>98613</t>
+          <t>97548</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>121763</t>
+          <t>121373</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>63,66%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>79,21%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>175896</t>
+          <t>175444</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>205691</t>
+          <t>204590</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>77,17%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>21128</t>
+          <t>21472</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>41786</t>
+          <t>41790</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>35871</t>
+          <t>35704</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>64478</t>
+          <t>64637</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>64740</t>
+          <t>62026</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>97913</t>
+          <t>97972</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,31%</t>
         </is>
       </c>
     </row>
@@ -4494,12 +4494,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>69664</t>
+          <t>69581</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>101492</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>135020</t>
+          <t>136953</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>179946</t>
+          <t>182362</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>213871</t>
+          <t>214501</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>269161</t>
+          <t>269046</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,81%</t>
         </is>
       </c>
     </row>
@@ -4607,12 +4607,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>370725</t>
+          <t>369604</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>405765</t>
+          <t>404284</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4622,12 +4622,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>73,78%</t>
+          <t>73,56%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>444617</t>
+          <t>442243</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>494833</t>
+          <t>492768</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>65,69%</t>
+          <t>65,34%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>827939</t>
+          <t>826571</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>888554</t>
+          <t>889077</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4692,12 +4692,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>70,21%</t>
+          <t>70,09%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,39%</t>
         </is>
       </c>
     </row>
@@ -4878,7 +4878,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si son capaces de realizar las tareas de la casa en 2012</t>
+          <t>Población según si son capaces de realizar las tareas de la casa en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5073,12 +5073,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>869</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8328</t>
+          <t>7866</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5088,12 +5088,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5108,12 +5108,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6045</t>
+          <t>5261</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17086</t>
+          <t>17187</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5123,12 +5123,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>7550</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21349</t>
+          <t>21224</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,78%</t>
         </is>
       </c>
     </row>
@@ -5186,12 +5186,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5506</t>
+          <t>6021</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16849</t>
+          <t>17227</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5201,12 +5201,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5221,12 +5221,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>10487</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>23897</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>48,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5256,12 +5256,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19331</t>
+          <t>18919</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37022</t>
+          <t>37841</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>40,61%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23811</t>
+          <t>23434</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>36233</t>
+          <t>36091</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>52,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15179</t>
+          <t>15022</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28865</t>
+          <t>28825</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>58,95%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>40950</t>
+          <t>42279</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>61384</t>
+          <t>62158</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>65,88%</t>
+          <t>66,71%</t>
         </is>
       </c>
     </row>
@@ -5529,12 +5529,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5359</t>
+          <t>5376</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19060</t>
+          <t>19218</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5564,12 +5564,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10684</t>
+          <t>10123</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>26825</t>
+          <t>26426</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5599,12 +5599,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>19401</t>
+          <t>18722</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>41042</t>
+          <t>38532</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5614,12 +5614,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>21,25%</t>
         </is>
       </c>
     </row>
@@ -5642,12 +5642,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6650</t>
+          <t>6595</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22870</t>
+          <t>22578</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5657,12 +5657,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5677,12 +5677,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14954</t>
+          <t>14941</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33231</t>
+          <t>32849</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5692,12 +5692,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5712,12 +5712,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>24884</t>
+          <t>25143</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>47890</t>
+          <t>48589</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5727,12 +5727,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,8%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>46081</t>
+          <t>45700</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>64141</t>
+          <t>63920</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>80,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>50478</t>
+          <t>51189</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>71137</t>
+          <t>71484</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>70,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>103398</t>
+          <t>102976</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>130788</t>
+          <t>130297</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>56,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>71,87%</t>
         </is>
       </c>
     </row>
@@ -5985,12 +5985,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3056</t>
+          <t>3053</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13667</t>
+          <t>15116</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6005,7 +6005,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6020,12 +6020,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5284</t>
+          <t>4461</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17327</t>
+          <t>16532</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6055,12 +6055,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>9820</t>
+          <t>9923</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>25993</t>
+          <t>26074</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6070,12 +6070,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,21%</t>
         </is>
       </c>
     </row>
@@ -6098,12 +6098,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>1044</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9174</t>
+          <t>9660</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6133,12 +6133,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7224</t>
+          <t>8070</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20620</t>
+          <t>21146</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6168,12 +6168,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10306</t>
+          <t>11212</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26540</t>
+          <t>27869</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>20,54%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>37335</t>
+          <t>36657</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>50109</t>
+          <t>50383</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>65,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>48357</t>
+          <t>48086</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>64576</t>
+          <t>63938</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,47%</t>
+          <t>60,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>90886</t>
+          <t>88257</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>110925</t>
+          <t>110460</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>65,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,39%</t>
         </is>
       </c>
     </row>
@@ -6441,12 +6441,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2913</t>
+          <t>3135</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13450</t>
+          <t>12897</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5334</t>
+          <t>5396</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17883</t>
+          <t>18156</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10436</t>
+          <t>10105</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26825</t>
+          <t>26710</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,85%</t>
         </is>
       </c>
     </row>
@@ -6554,12 +6554,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8804</t>
+          <t>8610</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22545</t>
+          <t>22346</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16106</t>
+          <t>16271</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32490</t>
+          <t>32786</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28368</t>
+          <t>28353</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>49921</t>
+          <t>49453</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,06%</t>
         </is>
       </c>
     </row>
@@ -6667,12 +6667,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>34724</t>
+          <t>34556</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>49578</t>
+          <t>49716</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>54,23%</t>
+          <t>53,97%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>41961</t>
+          <t>42135</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>60468</t>
+          <t>60099</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>70,66%</t>
+          <t>70,23%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>81337</t>
+          <t>82277</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>105385</t>
+          <t>105575</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6752,12 +6752,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>55,0%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>70,57%</t>
         </is>
       </c>
     </row>
@@ -6897,12 +6897,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1006</t>
+          <t>979</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8080</t>
+          <t>7960</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3171</t>
+          <t>3202</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13966</t>
+          <t>13514</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5307</t>
+          <t>5329</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>18015</t>
+          <t>17879</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>21,95%</t>
         </is>
       </c>
     </row>
@@ -7010,12 +7010,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2236</t>
+          <t>2161</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11136</t>
+          <t>11229</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8971</t>
+          <t>9299</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>22667</t>
+          <t>22333</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>13441</t>
+          <t>14074</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>28994</t>
+          <t>30237</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7095,12 +7095,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>37,12%</t>
         </is>
       </c>
     </row>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17406</t>
+          <t>17065</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27304</t>
+          <t>27489</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>53,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7158,12 +7158,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20165</t>
+          <t>20142</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>34132</t>
+          <t>33909</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>68,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7193,12 +7193,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>40943</t>
+          <t>40473</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>58238</t>
+          <t>57837</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7208,12 +7208,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>50,26%</t>
+          <t>49,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>71,49%</t>
+          <t>70,99%</t>
         </is>
       </c>
     </row>
@@ -7353,12 +7353,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>4296</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15010</t>
+          <t>15318</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6440</t>
+          <t>6448</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>19305</t>
+          <t>19155</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>12893</t>
+          <t>12962</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>30210</t>
+          <t>29944</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7438,12 +7438,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,55%</t>
         </is>
       </c>
     </row>
@@ -7466,12 +7466,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2156</t>
+          <t>2154</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12635</t>
+          <t>12611</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2119</t>
+          <t>1865</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11763</t>
+          <t>11762</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7516,7 +7516,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -7536,12 +7536,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6385</t>
+          <t>6233</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>20135</t>
+          <t>19329</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7551,12 +7551,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>15,85%</t>
         </is>
       </c>
     </row>
@@ -7579,12 +7579,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>30032</t>
+          <t>28729</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>43102</t>
+          <t>42499</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>55,51%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7614,12 +7614,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>44907</t>
+          <t>45504</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>59510</t>
+          <t>59561</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>63,96%</t>
+          <t>64,81%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7649,12 +7649,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>79316</t>
+          <t>79507</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>99236</t>
+          <t>98572</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7664,12 +7664,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>65,03%</t>
+          <t>65,19%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>80,82%</t>
         </is>
       </c>
     </row>
@@ -7809,12 +7809,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5959</t>
+          <t>5887</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>20351</t>
+          <t>20967</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7824,12 +7824,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7844,12 +7844,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>6144</t>
+          <t>6238</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>21474</t>
+          <t>20936</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7879,12 +7879,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>15009</t>
+          <t>14406</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>35334</t>
+          <t>34762</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7894,12 +7894,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,67%</t>
         </is>
       </c>
     </row>
@@ -7922,12 +7922,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>8258</t>
+          <t>8488</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>24912</t>
+          <t>25026</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7937,12 +7937,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7957,12 +7957,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>17957</t>
+          <t>18488</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>38157</t>
+          <t>37616</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7972,12 +7972,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7992,12 +7992,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>30013</t>
+          <t>30699</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>55337</t>
+          <t>55616</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,88%</t>
         </is>
       </c>
     </row>
@@ -8035,12 +8035,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>75361</t>
+          <t>76109</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>94892</t>
+          <t>95343</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>67,13%</t>
+          <t>67,8%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8070,12 +8070,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>90788</t>
+          <t>91484</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>113341</t>
+          <t>113179</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>64,44%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>79,72%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8105,12 +8105,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>173811</t>
+          <t>172928</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>202781</t>
+          <t>203254</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8120,12 +8120,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>68,02%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>79,95%</t>
         </is>
       </c>
     </row>
@@ -8265,12 +8265,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>1103</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>10793</t>
+          <t>10227</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8280,12 +8280,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8300,12 +8300,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>9165</t>
+          <t>9075</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>24642</t>
+          <t>24778</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8315,12 +8315,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8335,12 +8335,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>12226</t>
+          <t>13158</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>31001</t>
+          <t>31499</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8350,12 +8350,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,05%</t>
         </is>
       </c>
     </row>
@@ -8378,12 +8378,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>7697</t>
+          <t>7759</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>24639</t>
+          <t>23311</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8393,12 +8393,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>19928</t>
+          <t>19559</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>39827</t>
+          <t>39651</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8428,12 +8428,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>31761</t>
+          <t>31838</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>57956</t>
+          <t>57089</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8463,12 +8463,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,02%</t>
         </is>
       </c>
     </row>
@@ -8491,12 +8491,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>91676</t>
+          <t>91724</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>110608</t>
+          <t>109363</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8506,12 +8506,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>75,96%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>105927</t>
+          <t>106461</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>129876</t>
+          <t>130331</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8541,12 +8541,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>64,43%</t>
+          <t>64,75%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8561,12 +8561,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>206778</t>
+          <t>206269</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>235612</t>
+          <t>235882</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8576,12 +8576,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>72,33%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,72%</t>
         </is>
       </c>
     </row>
@@ -8721,12 +8721,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>41889</t>
+          <t>42443</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>71087</t>
+          <t>70021</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8736,12 +8736,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8756,12 +8756,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>78318</t>
+          <t>79103</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>115137</t>
+          <t>116736</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8771,12 +8771,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8791,12 +8791,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>128797</t>
+          <t>126783</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>177327</t>
+          <t>178036</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8806,12 +8806,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,67%</t>
         </is>
       </c>
     </row>
@@ -8834,12 +8834,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>67618</t>
+          <t>66302</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>104614</t>
+          <t>102908</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8849,12 +8849,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8869,12 +8869,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>131285</t>
+          <t>131518</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>176661</t>
+          <t>176386</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8884,12 +8884,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>208971</t>
+          <t>209938</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>268962</t>
+          <t>263875</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8919,12 +8919,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,26%</t>
         </is>
       </c>
     </row>
@@ -8947,12 +8947,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>397971</t>
+          <t>398943</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>441934</t>
+          <t>442326</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8962,12 +8962,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>71,29%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>468934</t>
+          <t>464219</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>519171</t>
+          <t>518613</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8997,12 +8997,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>69,8%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9017,12 +9017,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>882383</t>
+          <t>884710</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>949835</t>
+          <t>953322</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9032,12 +9032,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>67,74%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>72,92%</t>
+          <t>73,19%</t>
         </is>
       </c>
     </row>
@@ -9218,7 +9218,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si son capaces de realizar las tareas de la casa en 2016</t>
+          <t>Población según si son capaces de realizar las tareas de la casa en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9413,12 +9413,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2352</t>
+          <t>1676</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9686</t>
+          <t>9387</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9428,12 +9428,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9448,12 +9448,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1104</t>
+          <t>1111</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9864</t>
+          <t>10270</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4464</t>
+          <t>4764</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16193</t>
+          <t>15937</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,05%</t>
         </is>
       </c>
     </row>
@@ -9526,12 +9526,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1588</t>
+          <t>1587</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8432</t>
+          <t>8638</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9546,7 +9546,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9561,12 +9561,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9585</t>
+          <t>8806</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24400</t>
+          <t>23864</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9576,12 +9576,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9596,12 +9596,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12470</t>
+          <t>12416</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28997</t>
+          <t>29150</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9611,12 +9611,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>33,02%</t>
         </is>
       </c>
     </row>
@@ -9639,12 +9639,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24562</t>
+          <t>23751</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34001</t>
+          <t>34002</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9654,12 +9654,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>61,06%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9674,12 +9674,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>21068</t>
+          <t>21189</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>36353</t>
+          <t>36583</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9689,12 +9689,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9709,12 +9709,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>49117</t>
+          <t>48718</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>68190</t>
+          <t>66941</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9724,12 +9724,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>55,18%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>75,82%</t>
         </is>
       </c>
     </row>
@@ -9869,12 +9869,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10292</t>
+          <t>9506</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9889,7 +9889,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9904,12 +9904,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>5007</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>19167</t>
+          <t>18775</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9939,12 +9939,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7738</t>
+          <t>7819</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>23804</t>
+          <t>23968</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9954,12 +9954,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,83%</t>
         </is>
       </c>
     </row>
@@ -9982,12 +9982,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3721</t>
+          <t>4008</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13735</t>
+          <t>13864</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10017,12 +10017,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14965</t>
+          <t>13425</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>34344</t>
+          <t>33584</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10052,12 +10052,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>20769</t>
+          <t>20840</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>43144</t>
+          <t>43074</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10067,12 +10067,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,27%</t>
         </is>
       </c>
     </row>
@@ -10095,12 +10095,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>68498</t>
+          <t>68587</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>80827</t>
+          <t>80213</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>78,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>70645</t>
+          <t>69357</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>91393</t>
+          <t>92115</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>79,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10165,12 +10165,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>143854</t>
+          <t>142117</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>169666</t>
+          <t>168899</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10180,12 +10180,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>71,03%</t>
+          <t>70,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>83,4%</t>
         </is>
       </c>
     </row>
@@ -10325,12 +10325,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>737</t>
+          <t>741</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8259</t>
+          <t>9150</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10340,12 +10340,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10360,12 +10360,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1227</t>
+          <t>1245</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12285</t>
+          <t>12592</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10395,12 +10395,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3225</t>
+          <t>2905</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16501</t>
+          <t>15409</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10410,12 +10410,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>10,74%</t>
         </is>
       </c>
     </row>
@@ -10438,7 +10438,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6099</t>
+          <t>5548</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -10453,7 +10453,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -10473,12 +10473,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3308</t>
+          <t>3445</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14902</t>
+          <t>15481</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10488,12 +10488,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10508,12 +10508,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11689</t>
+          <t>11673</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27334</t>
+          <t>27825</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10523,12 +10523,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,4%</t>
         </is>
       </c>
     </row>
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>43954</t>
+          <t>43670</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>55760</t>
+          <t>55671</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>68,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>58974</t>
+          <t>57934</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>73863</t>
+          <t>73107</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>72,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10621,12 +10621,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>106533</t>
+          <t>107442</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>125739</t>
+          <t>126148</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10636,12 +10636,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,94%</t>
         </is>
       </c>
     </row>
@@ -10781,12 +10781,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2498</t>
+          <t>2465</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11050</t>
+          <t>10993</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10796,12 +10796,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10821,7 +10821,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8796</t>
+          <t>9146</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10836,7 +10836,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10851,12 +10851,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3734</t>
+          <t>3998</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15487</t>
+          <t>15498</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10866,12 +10866,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,92%</t>
         </is>
       </c>
     </row>
@@ -10894,12 +10894,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3769</t>
+          <t>4235</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15008</t>
+          <t>14230</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10909,12 +10909,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10929,12 +10929,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15442</t>
+          <t>14928</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34488</t>
+          <t>34177</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10964,12 +10964,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>21311</t>
+          <t>22374</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>43052</t>
+          <t>43949</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10979,12 +10979,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>28,12%</t>
         </is>
       </c>
     </row>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>43601</t>
+          <t>43983</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>56393</t>
+          <t>56017</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11022,12 +11022,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>67,97%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11042,12 +11042,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>54513</t>
+          <t>54299</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>74155</t>
+          <t>73654</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>59,53%</t>
+          <t>59,3%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>104914</t>
+          <t>103782</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>127647</t>
+          <t>126955</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>67,13%</t>
+          <t>66,41%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>81,23%</t>
         </is>
       </c>
     </row>
@@ -11237,12 +11237,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1676</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1097</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9239</t>
+          <t>8203</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11287,12 +11287,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1111</t>
+          <t>1115</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9361</t>
+          <t>8973</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11327,7 +11327,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>9,69%</t>
         </is>
       </c>
     </row>
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1652</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9353</t>
+          <t>9515</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11365,12 +11365,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11385,12 +11385,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8688</t>
+          <t>9272</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>21671</t>
+          <t>22860</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>45,24%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>12417</t>
+          <t>12293</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>28721</t>
+          <t>28907</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>31,21%</t>
         </is>
       </c>
     </row>
@@ -11463,12 +11463,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>32727</t>
+          <t>32565</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>40428</t>
+          <t>40088</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11478,12 +11478,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>77,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11498,12 +11498,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>25355</t>
+          <t>25090</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>38800</t>
+          <t>39443</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>78,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>60037</t>
+          <t>59980</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>77564</t>
+          <t>77269</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>64,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>83,43%</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5813</t>
+          <t>5824</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16276</t>
+          <t>16277</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11708,7 +11708,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3836</t>
+          <t>3978</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>18329</t>
+          <t>18243</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>12668</t>
+          <t>12471</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>29270</t>
+          <t>29043</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,07%</t>
         </is>
       </c>
     </row>
@@ -11806,12 +11806,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>820</t>
+          <t>830</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8318</t>
+          <t>7534</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11821,12 +11821,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11841,12 +11841,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3818</t>
+          <t>4185</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>17915</t>
+          <t>18256</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6289</t>
+          <t>6753</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>21354</t>
+          <t>21861</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,87%</t>
         </is>
       </c>
     </row>
@@ -11919,12 +11919,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>28224</t>
+          <t>28577</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>39937</t>
+          <t>40019</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11934,12 +11934,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11954,12 +11954,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>39959</t>
+          <t>38978</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>56504</t>
+          <t>56154</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11969,12 +11969,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>59,3%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>83,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11989,12 +11989,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>73141</t>
+          <t>72531</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>92631</t>
+          <t>92429</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12004,12 +12004,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>62,62%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>79,79%</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4545</t>
+          <t>4526</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>15777</t>
+          <t>16083</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5485</t>
+          <t>6077</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>19725</t>
+          <t>19586</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>12458</t>
+          <t>12817</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>30345</t>
+          <t>31864</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>12,26%</t>
         </is>
       </c>
     </row>
@@ -12262,12 +12262,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>10068</t>
+          <t>9966</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>25379</t>
+          <t>25916</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12277,12 +12277,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12297,12 +12297,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>28294</t>
+          <t>27981</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>50917</t>
+          <t>50713</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12312,12 +12312,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12332,12 +12332,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>42079</t>
+          <t>42426</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>69114</t>
+          <t>68676</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12347,12 +12347,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,43%</t>
         </is>
       </c>
     </row>
@@ -12375,12 +12375,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>76323</t>
+          <t>77065</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>94453</t>
+          <t>94593</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12390,12 +12390,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>68,69%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12410,12 +12410,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>85714</t>
+          <t>84558</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>109411</t>
+          <t>109260</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12425,12 +12425,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>57,28%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12445,12 +12445,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>168815</t>
+          <t>169320</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>199721</t>
+          <t>198320</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12460,12 +12460,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>65,17%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>76,33%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>4552</t>
+          <t>4239</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>17123</t>
+          <t>16570</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>1327</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>10770</t>
+          <t>10537</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12660,7 +12660,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>6683</t>
+          <t>7493</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>21621</t>
+          <t>22700</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -12718,12 +12718,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>6862</t>
+          <t>6938</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>20152</t>
+          <t>19917</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12733,12 +12733,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12753,12 +12753,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>38380</t>
+          <t>37596</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>66320</t>
+          <t>64516</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12768,12 +12768,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12788,12 +12788,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>48300</t>
+          <t>48832</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>80784</t>
+          <t>78065</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12803,12 +12803,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>25,14%</t>
         </is>
       </c>
     </row>
@@ -12831,12 +12831,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>102535</t>
+          <t>103907</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>119308</t>
+          <t>120262</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12846,12 +12846,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12866,12 +12866,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>106537</t>
+          <t>108253</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>135169</t>
+          <t>135372</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12881,12 +12881,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>61,4%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12901,12 +12901,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>218300</t>
+          <t>218890</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>250190</t>
+          <t>250615</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12916,12 +12916,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>80,72%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>35456</t>
+          <t>34856</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>58937</t>
+          <t>59064</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>35517</t>
+          <t>36563</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>65759</t>
+          <t>68298</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>77837</t>
+          <t>78253</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>116947</t>
+          <t>117884</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,61%</t>
         </is>
       </c>
     </row>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>54976</t>
+          <t>52557</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>83648</t>
+          <t>81906</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13189,12 +13189,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13209,12 +13209,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>159745</t>
+          <t>158314</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>207988</t>
+          <t>211570</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13224,12 +13224,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13244,12 +13244,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>222810</t>
+          <t>223373</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>283250</t>
+          <t>282504</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13259,12 +13259,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,63%</t>
         </is>
       </c>
     </row>
@@ -13287,12 +13287,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>461198</t>
+          <t>460230</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>495858</t>
+          <t>496806</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13302,12 +13302,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>77,99%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13322,12 +13322,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>516162</t>
+          <t>515861</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>572672</t>
+          <t>569273</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13337,12 +13337,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>66,31%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,18%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13357,12 +13357,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>982338</t>
+          <t>989697</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1053260</t>
+          <t>1052949</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13372,12 +13372,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>72,28%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>76,9%</t>
         </is>
       </c>
     </row>
@@ -13558,7 +13558,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si son capaces de realizar las tareas de la casa en 2023</t>
+          <t>Población según si son capaces de realizar las tareas de la casa en 2023 (tasa de respuesta: 99,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -13753,12 +13753,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2115</t>
+          <t>2261</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9637</t>
+          <t>9604</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -13768,12 +13768,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13788,12 +13788,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5930</t>
+          <t>5763</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14082</t>
+          <t>14419</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13803,12 +13803,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13823,12 +13823,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9371</t>
+          <t>8955</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20505</t>
+          <t>20760</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13838,12 +13838,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,4%</t>
         </is>
       </c>
     </row>
@@ -13866,12 +13866,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15106</t>
+          <t>15498</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27408</t>
+          <t>27177</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13881,12 +13881,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,03%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13901,12 +13901,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15591</t>
+          <t>15396</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25845</t>
+          <t>26121</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13916,12 +13916,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>41,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13936,12 +13936,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>33631</t>
+          <t>34281</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>49909</t>
+          <t>49854</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13951,12 +13951,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>41,79%</t>
         </is>
       </c>
     </row>
@@ -13979,12 +13979,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23671</t>
+          <t>23962</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>36079</t>
+          <t>35537</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13994,12 +13994,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>64,54%</t>
+          <t>63,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -14014,12 +14014,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27891</t>
+          <t>27611</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>38683</t>
+          <t>38847</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -14029,12 +14029,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>61,0%</t>
+          <t>61,26%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>54803</t>
+          <t>54953</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>71122</t>
+          <t>71510</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -14064,12 +14064,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>59,94%</t>
         </is>
       </c>
     </row>
@@ -14209,12 +14209,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3378</t>
+          <t>3387</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12559</t>
+          <t>12689</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -14224,12 +14224,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -14244,12 +14244,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13635</t>
+          <t>13843</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>25964</t>
+          <t>26156</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -14259,12 +14259,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -14279,12 +14279,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>18718</t>
+          <t>19229</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>34903</t>
+          <t>35492</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -14294,12 +14294,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,93%</t>
         </is>
       </c>
     </row>
@@ -14322,12 +14322,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2697</t>
+          <t>2583</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11735</t>
+          <t>12002</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -14337,12 +14337,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -14357,12 +14357,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>23844</t>
+          <t>24611</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>38469</t>
+          <t>38475</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -14372,12 +14372,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -14392,12 +14392,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>29391</t>
+          <t>29016</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>46623</t>
+          <t>46709</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -14407,12 +14407,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,27%</t>
         </is>
       </c>
     </row>
@@ -14435,12 +14435,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>61180</t>
+          <t>60286</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>73153</t>
+          <t>72891</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14450,12 +14450,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14470,12 +14470,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>70809</t>
+          <t>69603</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>87520</t>
+          <t>86708</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14485,12 +14485,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>53,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>67,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14505,12 +14505,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>135295</t>
+          <t>134088</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>155566</t>
+          <t>156830</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14520,12 +14520,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>74,79%</t>
         </is>
       </c>
     </row>
@@ -14665,12 +14665,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9841</t>
+          <t>10112</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20458</t>
+          <t>20873</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14700,12 +14700,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11784</t>
+          <t>12165</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>22152</t>
+          <t>23271</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14715,12 +14715,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14735,12 +14735,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>24601</t>
+          <t>24707</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>39227</t>
+          <t>39106</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,39%</t>
         </is>
       </c>
     </row>
@@ -14778,12 +14778,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3494</t>
+          <t>3381</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11780</t>
+          <t>11477</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -14793,12 +14793,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -14813,12 +14813,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15557</t>
+          <t>15528</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27231</t>
+          <t>27604</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -14828,12 +14828,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14848,12 +14848,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20864</t>
+          <t>21353</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34631</t>
+          <t>35630</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14863,12 +14863,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>22,22%</t>
         </is>
       </c>
     </row>
@@ -14891,12 +14891,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>45995</t>
+          <t>45796</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>57988</t>
+          <t>57387</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -14906,12 +14906,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>62,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>78,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14926,12 +14926,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>41966</t>
+          <t>42235</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>56023</t>
+          <t>56201</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -14941,12 +14941,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>48,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,5%</t>
+          <t>64,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14961,12 +14961,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>92333</t>
+          <t>91596</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>110319</t>
+          <t>109878</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -14976,12 +14976,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>57,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>68,52%</t>
         </is>
       </c>
     </row>
@@ -15121,12 +15121,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1111</t>
+          <t>1092</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6626</t>
+          <t>6471</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -15156,12 +15156,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6307</t>
+          <t>6317</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13635</t>
+          <t>13953</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -15171,12 +15171,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -15191,12 +15191,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8551</t>
+          <t>8384</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17704</t>
+          <t>17089</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -15206,12 +15206,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -15234,12 +15234,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8805</t>
+          <t>8681</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19395</t>
+          <t>19036</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -15269,12 +15269,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17245</t>
+          <t>17325</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27652</t>
+          <t>27689</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -15284,12 +15284,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15304,12 +15304,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28004</t>
+          <t>28677</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>43255</t>
+          <t>43475</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15319,12 +15319,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,38%</t>
         </is>
       </c>
     </row>
@@ -15347,12 +15347,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>52058</t>
+          <t>51782</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>63525</t>
+          <t>63069</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>69,35%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15382,12 +15382,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>66494</t>
+          <t>65720</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>77685</t>
+          <t>77254</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15397,12 +15397,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>63,41%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>74,54%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15417,12 +15417,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>122036</t>
+          <t>121373</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>137880</t>
+          <t>137766</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>68,07%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>77,27%</t>
         </is>
       </c>
     </row>
@@ -15577,12 +15577,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>487</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4148</t>
+          <t>4112</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -15597,7 +15597,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15612,12 +15612,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>698</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4225</t>
+          <t>4260</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15647,12 +15647,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1589</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6834</t>
+          <t>6366</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15662,12 +15662,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -15690,12 +15690,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2418</t>
+          <t>2469</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8157</t>
+          <t>8142</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -15705,12 +15705,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -15725,12 +15725,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8310</t>
+          <t>8512</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15966</t>
+          <t>15919</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -15740,12 +15740,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -15760,12 +15760,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>12161</t>
+          <t>12455</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>21471</t>
+          <t>21392</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -15775,12 +15775,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,74%</t>
         </is>
       </c>
     </row>
@@ -15803,12 +15803,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24938</t>
+          <t>24886</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>31274</t>
+          <t>31313</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15818,12 +15818,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>71,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15838,12 +15838,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>41324</t>
+          <t>40990</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>49191</t>
+          <t>49034</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15853,12 +15853,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>69,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15873,12 +15873,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>68592</t>
+          <t>68789</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>78647</t>
+          <t>78376</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15888,12 +15888,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>72,92%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>83,32%</t>
         </is>
       </c>
     </row>
@@ -16033,12 +16033,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8280</t>
+          <t>8735</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16433</t>
+          <t>16970</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -16048,12 +16048,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -16068,12 +16068,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>9938</t>
+          <t>10015</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>17707</t>
+          <t>18164</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -16083,12 +16083,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>20507</t>
+          <t>20585</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>31532</t>
+          <t>31617</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -16118,12 +16118,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,19%</t>
         </is>
       </c>
     </row>
@@ -16146,12 +16146,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6441</t>
+          <t>6961</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14156</t>
+          <t>14996</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -16161,12 +16161,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -16181,12 +16181,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10313</t>
+          <t>9944</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>17569</t>
+          <t>17535</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -16196,12 +16196,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -16216,12 +16216,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>18440</t>
+          <t>18803</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>29632</t>
+          <t>29873</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -16231,12 +16231,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,8%</t>
         </is>
       </c>
     </row>
@@ -16259,12 +16259,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>32536</t>
+          <t>32697</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>42907</t>
+          <t>42567</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -16274,12 +16274,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>53,99%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>71,2%</t>
+          <t>70,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -16294,12 +16294,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>32892</t>
+          <t>33169</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>42473</t>
+          <t>43025</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -16309,12 +16309,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>65,93%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -16329,12 +16329,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>68740</t>
+          <t>68601</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>82677</t>
+          <t>82176</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -16344,12 +16344,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>54,76%</t>
+          <t>54,65%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>65,47%</t>
         </is>
       </c>
     </row>
@@ -16489,12 +16489,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>722</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>8075</t>
+          <t>6620</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16509,7 +16509,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16524,12 +16524,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5209</t>
+          <t>5432</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>59293</t>
+          <t>60688</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16539,12 +16539,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16559,12 +16559,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6844</t>
+          <t>7393</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>48381</t>
+          <t>48825</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16574,12 +16574,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,57%</t>
         </is>
       </c>
     </row>
@@ -16602,12 +16602,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>7638</t>
+          <t>7448</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>19048</t>
+          <t>19465</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16617,12 +16617,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16637,12 +16637,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>7496</t>
+          <t>6115</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>71409</t>
+          <t>71430</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16652,12 +16652,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16672,12 +16672,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>11215</t>
+          <t>13244</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>73234</t>
+          <t>74002</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16687,12 +16687,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>16,03%</t>
         </is>
       </c>
     </row>
@@ -16715,12 +16715,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>100548</t>
+          <t>99343</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>113230</t>
+          <t>112614</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16730,12 +16730,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16750,12 +16750,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>212072</t>
+          <t>210846</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>325498</t>
+          <t>326666</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16765,12 +16765,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>62,16%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16785,12 +16785,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>343048</t>
+          <t>341681</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>443127</t>
+          <t>440103</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16800,12 +16800,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,32%</t>
         </is>
       </c>
     </row>
@@ -16945,12 +16945,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>769</t>
+          <t>938</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>6541</t>
+          <t>6049</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -16960,12 +16960,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -16980,12 +16980,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3919</t>
+          <t>3700</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>11980</t>
+          <t>12024</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -16995,12 +16995,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -17015,12 +17015,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5764</t>
+          <t>5865</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>15197</t>
+          <t>15353</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -17030,12 +17030,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -17058,12 +17058,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>6731</t>
+          <t>6434</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>16934</t>
+          <t>16239</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -17073,12 +17073,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -17093,12 +17093,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>32826</t>
+          <t>32425</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>50264</t>
+          <t>49071</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -17108,12 +17108,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -17128,12 +17128,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>42040</t>
+          <t>42025</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>61905</t>
+          <t>61354</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -17148,7 +17148,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,42%</t>
         </is>
       </c>
     </row>
@@ -17171,12 +17171,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>126879</t>
+          <t>126979</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>137972</t>
+          <t>137906</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -17186,12 +17186,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -17206,12 +17206,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>129995</t>
+          <t>130280</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>147444</t>
+          <t>147949</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -17221,12 +17221,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>69,8%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>79,0%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -17241,12 +17241,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>260470</t>
+          <t>261016</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>281695</t>
+          <t>281611</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -17256,12 +17256,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,54%</t>
         </is>
       </c>
     </row>
@@ -17401,12 +17401,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>39498</t>
+          <t>39042</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>59146</t>
+          <t>60578</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17416,12 +17416,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17436,12 +17436,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>53533</t>
+          <t>49995</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>128064</t>
+          <t>128406</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17451,12 +17451,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17471,12 +17471,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>95021</t>
+          <t>96701</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>175068</t>
+          <t>175081</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17486,7 +17486,7 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -17514,12 +17514,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>73485</t>
+          <t>72942</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>100588</t>
+          <t>99479</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17529,12 +17529,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17549,12 +17549,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>103087</t>
+          <t>93536</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>239566</t>
+          <t>238004</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17564,12 +17564,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17584,12 +17584,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>169144</t>
+          <t>178193</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>318879</t>
+          <t>318079</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17599,12 +17599,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,91%</t>
         </is>
       </c>
     </row>
@@ -17627,12 +17627,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>497829</t>
+          <t>497166</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>529399</t>
+          <t>529344</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -17642,12 +17642,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -17662,12 +17662,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>669504</t>
+          <t>671621</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>877374</t>
+          <t>885311</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -17677,12 +17677,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>64,8%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -17697,12 +17697,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1194324</t>
+          <t>1197340</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1418749</t>
+          <t>1409590</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -17712,12 +17712,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>71,18%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>83,8%</t>
         </is>
       </c>
     </row>
